--- a/templates_formats/Info_trabajador.xlsx
+++ b/templates_formats/Info_trabajador.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Fecha:</t>
   </si>
@@ -43,9 +43,6 @@
   </si>
   <si>
     <t>CORREO:</t>
-  </si>
-  <si>
-    <t>USUARIO ASIGNADO:</t>
   </si>
   <si>
     <t>CODIGO CARGO:</t>
@@ -514,24 +511,24 @@
   <sheetData>
     <row r="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D1" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D2" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D3" s="18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D4" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>0</v>
@@ -539,7 +536,7 @@
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D5" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E5" s="2"/>
       <c r="H5" s="1"/>
@@ -553,7 +550,7 @@
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D7" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2"/>
       <c r="H7" s="1"/>
@@ -610,11 +607,11 @@
       <c r="K11" s="1"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="D12" t="s">
+      <c r="D12" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>9</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>10</v>
       </c>
       <c r="F12" s="2"/>
       <c r="H12" s="1"/>
@@ -626,10 +623,10 @@
     <row r="13" spans="2:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="7"/>
       <c r="D13" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="11" t="s">
         <v>11</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>12</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
@@ -645,10 +642,10 @@
     <row r="14" spans="2:18" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="7"/>
       <c r="D14" s="11" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
@@ -663,11 +660,8 @@
     </row>
     <row r="15" spans="2:18" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="7"/>
-      <c r="D15" s="11" t="s">
-        <v>5</v>
-      </c>
       <c r="E15" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
@@ -699,7 +693,7 @@
     <row r="17" spans="3:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="7"/>
       <c r="D17" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
@@ -731,10 +725,10 @@
     <row r="19" spans="3:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C19" s="7"/>
       <c r="D19" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="11" t="s">
         <v>15</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>16</v>
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
@@ -750,7 +744,7 @@
     <row r="20" spans="3:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="7"/>
       <c r="D20" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E20" s="11"/>
       <c r="F20" s="7"/>

--- a/templates_formats/Info_trabajador.xlsx
+++ b/templates_formats/Info_trabajador.xlsx
@@ -140,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -170,28 +170,16 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="19"/>
+      <alignment horizontal="left" indent="27"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="27"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="26"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="21"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="23"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="18"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="16"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="12"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,10 +485,10 @@
   <dimension ref="A1:R69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.5" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="1" max="1" width="16.125" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="1.625" customWidth="1"/>
-    <col min="4" max="4" width="47.5" customWidth="1"/>
+    <col min="4" max="4" width="33.5" customWidth="1"/>
     <col min="5" max="5" width="22.625" customWidth="1"/>
     <col min="6" max="6" width="9.625" customWidth="1"/>
     <col min="7" max="7" width="9.25" customWidth="1"/>
@@ -509,56 +497,94 @@
     <col min="12" max="16" width="2.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="D1" s="16" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="D2" s="17" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
         <v>20</v>
       </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="D3" s="18" t="s">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="D4" s="19" t="s">
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D6" s="12"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="9" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="D5" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="H5" s="1"/>
-      <c r="K5" s="1"/>
-    </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="D6" s="13"/>
-      <c r="E6" s="2"/>
       <c r="H6" s="1"/>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="D7" s="14" t="s">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="H7" s="1"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E8" s="4"/>
       <c r="F8" s="2"/>
       <c r="H8" s="1"/>
@@ -566,7 +592,7 @@
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>6</v>
       </c>
@@ -582,7 +608,7 @@
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
         <v>3</v>
       </c>
@@ -593,7 +619,7 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
         <v>8</v>
       </c>
@@ -606,7 +632,7 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D12" s="11" t="s">
         <v>10</v>
       </c>
@@ -620,7 +646,7 @@
       <c r="K12" s="1"/>
       <c r="Q12" s="5"/>
     </row>
-    <row r="13" spans="2:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="7"/>
       <c r="D13" s="11" t="s">
         <v>4</v>
@@ -639,7 +665,7 @@
       <c r="P13" s="8"/>
       <c r="Q13" s="1"/>
     </row>
-    <row r="14" spans="2:18" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="7"/>
       <c r="D14" s="11" t="s">
         <v>5</v>
@@ -658,7 +684,7 @@
       <c r="P14" s="7"/>
       <c r="Q14" s="1"/>
     </row>
-    <row r="15" spans="2:18" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="7"/>
       <c r="E15" s="11" t="s">
         <v>13</v>
@@ -675,7 +701,7 @@
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
     </row>
-    <row r="16" spans="2:18" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="7"/>
       <c r="D16" s="11"/>
       <c r="E16" s="7"/>
@@ -690,15 +716,17 @@
       <c r="P16" s="7"/>
       <c r="Q16" s="1"/>
     </row>
-    <row r="17" spans="3:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="7"/>
-      <c r="D17" s="15" t="s">
+    <row r="17" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
       <c r="I17" s="1"/>
       <c r="L17" s="7"/>
       <c r="M17" s="7"/>
@@ -707,7 +735,7 @@
       <c r="P17" s="7"/>
       <c r="Q17" s="1"/>
     </row>
-    <row r="18" spans="3:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
@@ -722,7 +750,7 @@
       <c r="P18" s="7"/>
       <c r="Q18" s="1"/>
     </row>
-    <row r="19" spans="3:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C19" s="7"/>
       <c r="D19" s="11" t="s">
         <v>14</v>
@@ -741,7 +769,7 @@
       <c r="P19" s="7"/>
       <c r="Q19" s="1"/>
     </row>
-    <row r="20" spans="3:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="7"/>
       <c r="D20" s="11" t="s">
         <v>16</v>
@@ -758,7 +786,7 @@
       <c r="P20" s="7"/>
       <c r="Q20" s="1"/>
     </row>
-    <row r="21" spans="3:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="7"/>
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
@@ -773,7 +801,7 @@
       <c r="P21" s="7"/>
       <c r="Q21" s="1"/>
     </row>
-    <row r="22" spans="3:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="7"/>
       <c r="D22" s="11"/>
       <c r="E22" s="7"/>
@@ -788,7 +816,7 @@
       <c r="P22" s="7"/>
       <c r="Q22" s="1"/>
     </row>
-    <row r="23" spans="3:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
@@ -803,7 +831,7 @@
       <c r="P23" s="7"/>
       <c r="Q23" s="1"/>
     </row>
-    <row r="24" spans="3:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
@@ -818,7 +846,7 @@
       <c r="P24" s="7"/>
       <c r="Q24" s="1"/>
     </row>
-    <row r="25" spans="3:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
@@ -833,7 +861,7 @@
       <c r="P25" s="7"/>
       <c r="Q25" s="1"/>
     </row>
-    <row r="26" spans="3:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
@@ -849,7 +877,7 @@
       <c r="P26" s="7"/>
       <c r="Q26" s="1"/>
     </row>
-    <row r="27" spans="3:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
@@ -858,7 +886,7 @@
       <c r="H27" s="7"/>
       <c r="I27" s="1"/>
     </row>
-    <row r="28" spans="3:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
@@ -867,7 +895,7 @@
       <c r="H28" s="7"/>
       <c r="I28" s="1"/>
     </row>
-    <row r="29" spans="3:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
@@ -876,7 +904,7 @@
       <c r="H29" s="7"/>
       <c r="I29" s="1"/>
     </row>
-    <row r="30" spans="3:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
@@ -885,7 +913,7 @@
       <c r="H30" s="7"/>
       <c r="I30" s="1"/>
     </row>
-    <row r="31" spans="3:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
@@ -894,7 +922,7 @@
       <c r="H31" s="7"/>
       <c r="I31" s="1"/>
     </row>
-    <row r="32" spans="3:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
@@ -1143,6 +1171,15 @@
       <c r="Q69" s="1"/>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A7:H7"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="172" orientation="landscape" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
